--- a/consent_forms/035_personal_care_agreement--consent_forms.xlsx
+++ b/consent_forms/035_personal_care_agreement--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name of person responsible for care</t>
+          <t>Personal Care Agreement 1 Responsible Caregiver Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What needs do we need to take care of?</t>
+          <t>Personal Care Agreement 1 Client Needs Hint</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical Needs</t>
+          <t>Personal Care Agreement 1 Medical Needs Hint</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical Needs Details</t>
+          <t>Personal Care Agreement 1 Medical Needs Details Hint</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Caregiver Needs</t>
+          <t>Personal Care Agreement 1 Caregiver Needs Hint</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Caregiver Needs Details</t>
+          <t>Personal Care Agreement 1 Caregiver Needs Details Hint</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other Needs</t>
+          <t>Personal Care Agreement 1 Other Needs Hint</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other Needs Details</t>
+          <t>Personal Care Agreement 1 Other Needs Details Hint</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Agreement Terms</t>
+          <t>Personal Care Agreement 1 Agreement Terms Hint</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
